--- a/homework2.xlsx
+++ b/homework2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tihitinazergaw\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78267B80-4E25-4EDB-95F6-A2C55FEE21D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A02F7D4-5A80-46D1-AA91-31B0FD69184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5D97EBD8-5C2D-40D1-8CDD-E83CB42287B9}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -190,14 +190,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -329,6 +328,82 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="25400">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="25400">
+            <a:contourClr>
+              <a:schemeClr val="lt1"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="25400">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="25400">
+            <a:contourClr>
+              <a:schemeClr val="lt1"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="25400">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="25400">
+            <a:contourClr>
+              <a:schemeClr val="lt1"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="25400">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="25400">
+            <a:contourClr>
+              <a:schemeClr val="lt1"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
       <c:rotX val="30"/>
@@ -406,6 +481,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4880-4D52-992C-03D86C501135}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -426,6 +506,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4880-4D52-992C-03D86C501135}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -446,6 +531,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4880-4D52-992C-03D86C501135}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -466,6 +556,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-4880-4D52-992C-03D86C501135}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2368,7 +2463,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7BBB5B3-64B5-445D-9317-CA0EAE650F1F}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7BBB5B3-64B5-445D-9317-CA0EAE650F1F}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="G24:H28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -2430,7 +2525,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A4D110F-DC72-4B1B-8F0C-61C69407AD48}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A4D110F-DC72-4B1B-8F0C-61C69407AD48}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="G1:H6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -2472,12 +2567,60 @@
   <dataFields count="1">
     <dataField name="Sum of Monthly Sales" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="5">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -2858,7 +3001,7 @@
       <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>145</v>
       </c>
     </row>
@@ -2878,7 +3021,7 @@
       <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>138</v>
       </c>
     </row>
@@ -2898,7 +3041,7 @@
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>143</v>
       </c>
     </row>
@@ -2918,7 +3061,7 @@
       <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>167</v>
       </c>
     </row>
@@ -2938,7 +3081,7 @@
       <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>593</v>
       </c>
     </row>
@@ -3078,7 +3221,7 @@
       <c r="G25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25">
         <v>195</v>
       </c>
     </row>
@@ -3086,7 +3229,7 @@
       <c r="G26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26">
         <v>218</v>
       </c>
     </row>
@@ -3094,7 +3237,7 @@
       <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27">
         <v>180</v>
       </c>
     </row>
@@ -3102,7 +3245,7 @@
       <c r="G28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28">
         <v>593</v>
       </c>
     </row>
@@ -3122,7 +3265,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3138,7 +3281,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
